--- a/quizzes/046_wedding_dress_quiz--quizzes.xlsx
+++ b/quizzes/046_wedding_dress_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ball_gown</t>
+          <t>ball gown</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mermaid_maison</t>
+          <t>mermaid maison</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ball_gown_maison</t>
+          <t>ball gown maison</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tea_party</t>
+          <t>tea party</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>off_the_shelf</t>
+          <t>off the shelf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tea_party</t>
+          <t>tea party</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>knee_length</t>
+          <t>knee length</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>floor_length</t>
+          <t>floor length</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ivory_beaded</t>
+          <t>ivory beaded</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ivory_champagne</t>
+          <t>ivory champagne</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ivory_silk</t>
+          <t>ivory silk</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ivory_tulle</t>
+          <t>ivory tulle</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ivory_beaded_satin</t>
+          <t>ivory beaded satin</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ivory_draped</t>
+          <t>ivory draped</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ivory_solid</t>
+          <t>ivory solid</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ivory_beaded_champagne</t>
+          <t>ivory beaded champagne</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ivory_champagne</t>
+          <t>ivory_draped_champagne</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ivory_champagne</t>
+          <t>ivory draped champagne</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ivory_draped_champagne</t>
+          <t>ivory_solid_champagne</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ivory_draped_champagne</t>
+          <t>ivory solid champagne</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ivory_solid_champagne</t>
+          <t>beige_tulle</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ivory_solid_champagne</t>
+          <t>beige tulle</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>beige_tulle</t>
+          <t>beige_lace</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>beige_tulle</t>
+          <t>beige lace</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>beige_lace</t>
+          <t>beige_beaded</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>beige_lace</t>
+          <t>beige beaded</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>beige_beaded</t>
+          <t>beige_champagne</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>beige_beaded</t>
+          <t>beige champagne</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>beige_champagne</t>
+          <t>beige_draped</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>beige_champagne</t>
+          <t>beige draped</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>beige_draped</t>
+          <t>beige_solid</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>beige_draped</t>
+          <t>beige solid</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>beige_solid</t>
+          <t>beige_lace_champagne</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>beige_solid</t>
+          <t>beige lace champagne</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>beige_tulle</t>
+          <t>ivory_beaded_tulle</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>beige_tulle</t>
+          <t>ivory beaded tulle</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>beige_lace_champagne</t>
+          <t>ivory_lace</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>beige_lace_champagne</t>
+          <t>ivory lace</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ivory_beaded_tulle</t>
+          <t>ivory_beaded_lace</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ivory_beaded_tulle</t>
+          <t>ivory beaded lace</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ivory_tulle</t>
+          <t>ivory_lace_champagne</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ivory_tulle</t>
+          <t>ivory lace champagne</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ivory_lace</t>
+          <t>ivory_tulle_champagne</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ivory_lace</t>
+          <t>ivory tulle champagne</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ivory_beaded_lace</t>
+          <t>ivory_solid_tulle</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ivory_beaded_lace</t>
+          <t>ivory solid tulle</t>
         </is>
       </c>
     </row>
@@ -1596,63 +1596,63 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ivory_lace_champagne</t>
+          <t>ivory_tulle_lace</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ivory_lace_champagne</t>
+          <t>ivory tulle lace</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>wedding_color_choices</t>
+          <t>favorite_feature_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ivory_tulle_champagne</t>
+          <t>beaded</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ivory_tulle_champagne</t>
+          <t>beaded</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>wedding_color_choices</t>
+          <t>favorite_feature_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ivory_solid_tulle</t>
+          <t>appliques</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ivory_solid_tulle</t>
+          <t>appliques</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>wedding_color_choices</t>
+          <t>favorite_feature_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ivory_tulle_lace</t>
+          <t>appliques_1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ivory_tulle_lace</t>
+          <t>appliques 1</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>beaded</t>
+          <t>appliques_2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>beaded</t>
+          <t>appliques 2</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>appliques</t>
+          <t>appliques_3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>appliques</t>
+          <t>appliques 3</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>appliques</t>
+          <t>appliques_4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>appliques</t>
+          <t>appliques 4</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>appliques_1</t>
+          <t>appliques_5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>appliques_1</t>
+          <t>appliques 5</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>appliques_2</t>
+          <t>appliques_6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>appliques_2</t>
+          <t>appliques 6</t>
         </is>
       </c>
     </row>
@@ -1749,80 +1749,80 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>appliques_3</t>
+          <t>appliques_7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>appliques_3</t>
+          <t>appliques 7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>overall_feeling_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>appliques_4</t>
+          <t>romantic</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>appliques_4</t>
+          <t>romantic</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>overall_feeling_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>appliques_5</t>
+          <t>classy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>appliques_5</t>
+          <t>classy</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>overall_feeling_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>appliques_6</t>
+          <t>feminine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>appliques_6</t>
+          <t>feminine</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>overall_feeling_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>appliques_7</t>
+          <t>feminist</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>appliques_7</t>
+          <t>feminist</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>romantic</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>romantic</t>
+          <t>strong</t>
         </is>
       </c>
     </row>
@@ -1851,112 +1851,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>classy</t>
+          <t>strong_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>classy</t>
+          <t>strong 2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>overall_feeling_choices</t>
+          <t>comfort_level_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>feminine</t>
+          <t>comfortable</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>feminine</t>
+          <t>comfortable</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>overall_feeling_choices</t>
+          <t>comfort_level_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>feminist</t>
+          <t>uncomfortable</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
-        <is>
-          <t>feminist</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>overall_feeling_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>overall_feeling_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>strong_2</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>strong_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>comfort_level_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>comfortable</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>comfortable</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>comfort_level_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>uncomfortable</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
         <is>
           <t>uncomfortable</t>
         </is>
